--- a/excel_config/indir/炼丹.xlsx
+++ b/excel_config/indir/炼丹.xlsx
@@ -1178,12 +1178,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>[{"family":"灵草","count":2,"weight":2,"options":[{"id":"items_LingCao","quality":1},{"id":"items_LingCao_Fine","quality":2},{"id":"items_LingCao_Superior","quality":3}]}]</t>
+          <t>[{"family": "灵草", "count": 2, "weight": 2, "options": [{"id": "items_LingCao", "quality": 1}, {"id": "items_LingCao_Fine", "quality": 2}, {"id": "items_LingCao_Superior", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>{"low":"items_HuiQiDan_Low","medium":"items_HuiQiDan","high":"items_HuiQiDan_High","supreme":"items_HuiQiDan_Supreme"}</t>
+          <t>{"low": "items_HuiQiDan_Low", "medium": "items_HuiQiDan", "high": "items_HuiQiDan_High", "supreme": "items_HuiQiDan_Supreme"}</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>[{"family":"灵草","count":1,"weight":2,"options":[{"id":"items_LingCao","quality":1},{"id":"items_LingCao_Fine","quality":2},{"id":"items_LingCao_Superior","quality":3}]},{"family":"灵果","count":1,"weight":1,"options":[{"id":"items_LingGuo","quality":1},{"id":"items_LingGuo_Fine","quality":2},{"id":"items_LingGuo_Superior","quality":3}]}]</t>
+          <t>[{"family": "灵草", "count": 1, "weight": 2, "options": [{"id": "items_LingCao", "quality": 1}, {"id": "items_LingCao_Fine", "quality": 2}, {"id": "items_LingCao_Superior", "quality": 3}]}, {"family": "灵果", "count": 1, "weight": 1, "options": [{"id": "items_LingGuo", "quality": 1}, {"id": "items_LingGuo_Fine", "quality": 2}, {"id": "items_LingGuo_Superior", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>{"low":"items_HuiLingDan_Low","medium":"items_HuiLingDan","high":"items_HuiLingDan_High","supreme":"items_HuiLingDan_Supreme"}</t>
+          <t>{"low": "items_HuiLingDan_Low", "medium": "items_HuiLingDan", "high": "items_HuiLingDan_High", "supreme": "items_HuiLingDan_Supreme"}</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>[{"family":"灵草","count":2,"weight":2,"options":[{"id":"items_LingCao","quality":1},{"id":"items_LingCao_Fine","quality":2},{"id":"items_LingCao_Superior","quality":3}]},{"family":"灵果","count":1,"weight":1,"options":[{"id":"items_LingGuo","quality":1},{"id":"items_LingGuo_Fine","quality":2},{"id":"items_LingGuo_Superior","quality":3}]}]</t>
+          <t>[{"family": "灵草", "count": 2, "weight": 2, "options": [{"id": "items_LingCao", "quality": 1}, {"id": "items_LingCao_Fine", "quality": 2}, {"id": "items_LingCao_Superior", "quality": 3}]}, {"family": "灵果", "count": 1, "weight": 1, "options": [{"id": "items_LingGuo", "quality": 1}, {"id": "items_LingGuo_Fine", "quality": 2}, {"id": "items_LingGuo_Superior", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>{"low":"items_LiaoShangDan_Low","medium":"items_LiaoShangDan","high":"items_LiaoShangDan_High","supreme":"items_LiaoShangDan_Supreme"}</t>
+          <t>{"low": "items_LiaoShangDan_Low", "medium": "items_LiaoShangDan", "high": "items_LiaoShangDan_High", "supreme": "items_LiaoShangDan_Supreme"}</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>[{"family":"灵草","count":2,"weight":2,"options":[{"id":"items_LingCao","quality":1},{"id":"items_LingCao_Fine","quality":2},{"id":"items_LingCao_Superior","quality":3}]},{"family":"灵果","count":1,"weight":1,"options":[{"id":"items_LingGuo","quality":1},{"id":"items_LingGuo_Fine","quality":2},{"id":"items_LingGuo_Superior","quality":3}]},{"family":"妖丹","count":1,"weight":1,"options":[{"id":"items_YaoDan","quality":3}]}]</t>
+          <t>[{"family": "灵草", "count": 2, "weight": 2, "options": [{"id": "items_LingCao", "quality": 1}, {"id": "items_LingCao_Fine", "quality": 2}, {"id": "items_LingCao_Superior", "quality": 3}]}, {"family": "灵果", "count": 1, "weight": 1, "options": [{"id": "items_LingGuo", "quality": 1}, {"id": "items_LingGuo_Fine", "quality": 2}, {"id": "items_LingGuo_Superior", "quality": 3}]}, {"family": "妖丹", "count": 1, "weight": 1, "options": [{"id": "items_YaoDan", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>{"low":"items_JuQiDan_Low","medium":"items_JuQiDan","high":"items_JuQiDan_High","supreme":"items_JuQiDan_Supreme"}</t>
+          <t>{"low": "items_JuQiDan_Low", "medium": "items_JuQiDan", "high": "items_JuQiDan_High", "supreme": "items_JuQiDan_Supreme"}</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>[{"family":"雾隐草","count":2,"weight":2,"options":[{"id":"items_MistHerb","quality":2},{"id":"items_MistHerb_Fine","quality":3}]},{"family":"灵果","count":1,"weight":1,"options":[{"id":"items_LingGuo","quality":1},{"id":"items_LingGuo_Fine","quality":2},{"id":"items_LingGuo_Superior","quality":3}]}]</t>
+          <t>[{"family": "雾隐草", "count": 2, "weight": 2, "options": [{"id": "items_MistHerb", "quality": 2}, {"id": "items_MistHerb_Fine", "quality": 3}]}, {"family": "灵果", "count": 1, "weight": 1, "options": [{"id": "items_LingGuo", "quality": 1}, {"id": "items_LingGuo_Fine", "quality": 2}, {"id": "items_LingGuo_Superior", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>{"low":"items_QingMaiDan_Low","medium":"items_QingMaiDan","high":"items_QingMaiDan_High","supreme":"items_QingMaiDan_Supreme"}</t>
+          <t>{"low": "items_QingMaiDan_Low", "medium": "items_QingMaiDan", "high": "items_QingMaiDan_High", "supreme": "items_QingMaiDan_Supreme"}</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>[{"family":"雾隐草","count":2,"weight":2,"options":[{"id":"items_MistHerb","quality":2},{"id":"items_MistHerb_Fine","quality":3}]},{"family":"妖丹","count":1,"weight":1,"options":[{"id":"items_YaoDan","quality":3}]},{"family":"阵核碎片","count":1,"weight":2,"options":[{"id":"items_ArrayCoreShard","quality":3}]}]</t>
+          <t>[{"family": "雾隐草", "count": 2, "weight": 2, "options": [{"id": "items_MistHerb", "quality": 2}, {"id": "items_MistHerb_Fine", "quality": 3}]}, {"family": "妖丹", "count": 1, "weight": 1, "options": [{"id": "items_YaoDan", "quality": 3}]}, {"family": "阵核碎片", "count": 1, "weight": 2, "options": [{"id": "items_ArrayCoreShard", "quality": 3}]}]</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>{"low":"items_GuBenDaoJiDan_Low","medium":"items_GuBenDaoJiDan","high":"items_GuBenDaoJiDan_High","supreme":"items_GuBenDaoJiDan_Supreme"}</t>
+          <t>{"low": "items_GuBenDaoJiDan_Low", "medium": "items_GuBenDaoJiDan", "high": "items_GuBenDaoJiDan_High", "supreme": "items_GuBenDaoJiDan_Supreme"}</t>
         </is>
       </c>
     </row>
